--- a/artfynd/S 488-2024 artfynd.xlsx
+++ b/artfynd/S 488-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY96"/>
+  <dimension ref="A1:AZ96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89122986</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89123002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89122985</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89122987</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89122990</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89122991</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89122993</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89122994</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89122997</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89123003</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89123254</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89122996</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1985,6 +2050,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89123001</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2086,6 +2156,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89123253</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2187,6 +2262,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89123258</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2288,6 +2368,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89122999</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2389,6 +2474,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89122988</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2499,6 +2589,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89123255</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2600,6 +2695,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89122982</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2701,6 +2801,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89122983</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2802,6 +2907,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89122992</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2903,6 +3013,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89122995</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3004,6 +3119,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89123004</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3105,6 +3225,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89123257</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3206,6 +3331,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89123260</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3307,6 +3437,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89123261</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3408,6 +3543,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89123288</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3513,6 +3653,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89123251</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3618,6 +3763,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89123256</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3719,6 +3869,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89123250</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3820,6 +3975,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89119779</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3921,6 +4081,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89123020</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4022,6 +4187,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89123021</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4123,6 +4293,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89124207</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4224,6 +4399,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89124205</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4325,6 +4505,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89124252</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4426,6 +4611,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89124250</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4527,6 +4717,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89124251</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4641,6 +4836,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89124779</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4761,6 +4961,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93542725</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4862,6 +5067,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89124778</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4963,6 +5173,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89123598</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5064,6 +5279,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89123599</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5166,6 +5386,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89123100</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5267,6 +5492,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89123090</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5364,6 +5594,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89119367</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5461,6 +5696,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89119368</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5558,6 +5798,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89119370</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5655,6 +5900,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89123101</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5752,6 +6002,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89123103</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5849,6 +6104,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89123104</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5950,6 +6210,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89123603</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6051,6 +6316,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89123600</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6176,6 +6446,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93542749</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6296,6 +6571,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93542712</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6416,6 +6696,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93542713</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6517,6 +6802,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89124013</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6618,6 +6908,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89124006</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6728,6 +7023,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89124007</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6829,6 +7129,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89123994</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6930,6 +7235,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89124010</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7031,6 +7341,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89124012</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7132,6 +7447,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89124011</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7249,6 +7569,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89125218</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7353,6 +7678,11 @@
       <c r="AY66" t="inlineStr">
         <is>
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
+        </is>
+      </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89125219</t>
         </is>
       </c>
     </row>
@@ -7475,6 +7805,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89114858</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7598,6 +7933,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89114902</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7719,6 +8059,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89114897</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7820,6 +8165,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89114899</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7926,6 +8276,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89114890</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8042,6 +8397,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93803032</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8143,6 +8503,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89114886</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8257,6 +8622,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89114904</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8371,6 +8741,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89114909</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8485,6 +8860,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89114917</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8599,6 +8979,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89114936</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8713,6 +9098,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89114888</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8827,6 +9217,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89114892</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8933,6 +9328,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89114921</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9034,6 +9434,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89114931</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9135,6 +9540,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89114856</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9236,6 +9646,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89114860</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9342,6 +9757,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89114939</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9443,6 +9863,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89114854</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9544,6 +9969,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89114863</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9658,6 +10088,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89114865</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9768,6 +10203,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89117414</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9865,6 +10305,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89117413</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9962,6 +10407,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89122843</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10060,6 +10510,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89122845</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10161,6 +10616,11 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89124374</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10258,6 +10718,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89122844</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10355,6 +10820,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89122842</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10452,6 +10922,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89122846</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10553,8 +11028,110 @@
           <t>Naturvärdesinventering inför Källmyrbergets vindpark</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89123781</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>